--- a/utils/monday_sprint_sprint_2025-6.xlsx
+++ b/utils/monday_sprint_sprint_2025-6.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="179">
   <si>
     <t>Ticket</t>
   </si>
@@ -189,7 +189,7 @@
     <t>15/10/2024</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Fevereiro</t>
@@ -2771,7 +2774,7 @@
         <v>111</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>20</v>
@@ -2780,7 +2783,7 @@
         <v>25</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -2797,10 +2800,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -2829,7 +2832,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -2841,10 +2844,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -2885,7 +2888,7 @@
         <v>52</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>108</v>
@@ -2903,7 +2906,7 @@
         <v>111</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>20</v>
@@ -2912,7 +2915,7 @@
         <v>25</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -2929,10 +2932,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -2961,7 +2964,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -2973,22 +2976,22 @@
         <v>52</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>17</v>
@@ -3000,12 +3003,12 @@
         <v>25</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3017,10 +3020,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>75</v>
@@ -3038,7 +3041,7 @@
         <v>17</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>98</v>
@@ -3049,7 +3052,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3061,39 +3064,39 @@
         <v>52</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3105,10 +3108,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3137,7 +3140,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3149,10 +3152,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>75</v>
@@ -3181,7 +3184,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3193,10 +3196,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>75</v>
@@ -3214,7 +3217,7 @@
         <v>17</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>25</v>
@@ -3225,7 +3228,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3237,10 +3240,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>75</v>
@@ -3281,7 +3284,7 @@
         <v>52</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>108</v>
@@ -3299,7 +3302,7 @@
         <v>111</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>20</v>
@@ -3308,7 +3311,7 @@
         <v>25</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -3325,7 +3328,7 @@
         <v>52</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>108</v>
@@ -3343,7 +3346,7 @@
         <v>111</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>20</v>
@@ -3352,7 +3355,7 @@
         <v>25</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -3369,7 +3372,7 @@
         <v>52</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>108</v>
@@ -3387,7 +3390,7 @@
         <v>111</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>20</v>
@@ -3396,7 +3399,7 @@
         <v>25</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -3413,7 +3416,7 @@
         <v>52</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>108</v>
@@ -3431,7 +3434,7 @@
         <v>111</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
@@ -3440,7 +3443,7 @@
         <v>25</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -3457,7 +3460,7 @@
         <v>52</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>108</v>
@@ -3475,7 +3478,7 @@
         <v>111</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>20</v>
@@ -3484,7 +3487,7 @@
         <v>25</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -3501,7 +3504,7 @@
         <v>52</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>108</v>
@@ -3519,7 +3522,7 @@
         <v>111</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>20</v>
@@ -3528,7 +3531,7 @@
         <v>25</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -3545,10 +3548,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3589,10 +3592,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3632,23 +3635,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3656,16 +3659,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3684,7 +3687,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3697,7 +3700,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3705,7 +3708,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3736,12 +3739,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B2">
         <v>59</v>
@@ -3765,25 +3768,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3800,13 +3803,13 @@
         <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3838,13 +3841,13 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K11">
         <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3853,7 +3856,7 @@
         <v>25</v>
       </c>
       <c r="Q11">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3870,7 +3873,7 @@
         <v>50</v>
       </c>
       <c r="M12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3879,7 +3882,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -3890,7 +3893,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3905,32 +3908,26 @@
         <v>98</v>
       </c>
       <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -3938,7 +3935,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3946,7 +3943,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3954,7 +3951,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -3965,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3979,7 +3976,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>53</v>
@@ -3993,7 +3990,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>62</v>
@@ -4001,7 +3998,7 @@
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -4010,7 +4007,7 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4021,24 +4018,24 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4049,10 +4046,10 @@
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4063,10 +4060,10 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4077,10 +4074,10 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4091,10 +4088,10 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4105,10 +4102,10 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-6.xlsx
+++ b/utils/monday_sprint_sprint_2025-6.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="207">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30113</t>
+    <t>8540149825</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>21/02/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>12/03/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>29478</t>
+    <t>8657857430</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Venda Geral</t>
@@ -111,19 +111,19 @@
     <t>10/03/2025</t>
   </si>
   <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Março</t>
   </si>
   <si>
-    <t>30296</t>
+    <t>8648287159</t>
   </si>
   <si>
     <t>Inclusão - Relatório Situação Deposito WMS</t>
@@ -132,22 +132,31 @@
     <t>07/03/2025</t>
   </si>
   <si>
+    <t>11/03/2025</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>30158</t>
+    <t>8539935888</t>
   </si>
   <si>
     <t>CADASTRO DE DOCUMENTO NO SETOR 500</t>
   </si>
   <si>
-    <t>29781</t>
+    <t>19/03/2025</t>
+  </si>
+  <si>
+    <t>8648433272</t>
   </si>
   <si>
     <t>Embalagens qlik sense</t>
   </si>
   <si>
-    <t>30418</t>
+    <t>13/03/2025</t>
+  </si>
+  <si>
+    <t>8659468663</t>
   </si>
   <si>
     <t>Correção</t>
@@ -156,13 +165,16 @@
     <t>Irog ajustagem</t>
   </si>
   <si>
-    <t>30335</t>
+    <t>20/03/2025</t>
+  </si>
+  <si>
+    <t>8657940437</t>
   </si>
   <si>
     <t>Melhorias apontamento jato</t>
   </si>
   <si>
-    <t>26634</t>
+    <t>6973572944</t>
   </si>
   <si>
     <t>Migrar aplicação para o Qliksense - Rendimento de Projeto</t>
@@ -174,31 +186,31 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>30280</t>
+    <t>8648374144</t>
   </si>
   <si>
     <t>Informações DOA</t>
   </si>
   <si>
-    <t>30245</t>
+    <t>8648387689</t>
   </si>
   <si>
     <t>ADICIONAR MOTIVO DE PARADA MANIPULADOR REB. VI - "TROCA DE REBOLO/DISCO" - no apontamento do tablet do operador!</t>
   </si>
   <si>
-    <t>30438</t>
+    <t>8659476908</t>
   </si>
   <si>
     <t>Irog ajustagem I</t>
   </si>
   <si>
-    <t>30112</t>
+    <t>8540162347</t>
   </si>
   <si>
     <t>BLOQUEIO DE RESPOSTAS EM BRANCO NA AC</t>
   </si>
   <si>
-    <t>30139</t>
+    <t>8540092249</t>
   </si>
   <si>
     <t>Separar permissão transferência para o estoque intermediário</t>
@@ -207,6 +219,9 @@
     <t>28392</t>
   </si>
   <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
     <t>Projeto</t>
   </si>
   <si>
@@ -228,7 +243,7 @@
     <t>24/03/2026</t>
   </si>
   <si>
-    <t>30038</t>
+    <t>8648462715</t>
   </si>
   <si>
     <t>Liberação para ordem de segurança</t>
@@ -237,37 +252,40 @@
     <t>Notas de consignado - Medição NIMBI</t>
   </si>
   <si>
-    <t>29795</t>
+    <t>8657705255</t>
   </si>
   <si>
     <t>Relatório de modelos com tempo sem uso</t>
   </si>
   <si>
-    <t>30393</t>
+    <t>18/03/2025</t>
+  </si>
+  <si>
+    <t>8648063794</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Contabilização por item</t>
   </si>
   <si>
-    <t>30218</t>
+    <t>8657705185</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Devolução de compra - Centro de Custo</t>
   </si>
   <si>
-    <t>27940</t>
+    <t>8648520142</t>
   </si>
   <si>
     <t>QVD de extração</t>
   </si>
   <si>
-    <t>28956</t>
+    <t>8657750791</t>
   </si>
   <si>
     <t>Montar relatório de pendências (filtro por status)</t>
   </si>
   <si>
-    <t>30454</t>
+    <t>8648477607</t>
   </si>
   <si>
     <t>Ocultar Consertos de Modelo - Modelo 84E902436ABG1</t>
@@ -276,37 +294,52 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>30366</t>
+    <t>8648171090</t>
   </si>
   <si>
     <t>Pré-Lista EPI</t>
   </si>
   <si>
-    <t>30373</t>
+    <t>8668303620</t>
   </si>
   <si>
     <t>Substituir cotas de PDI em andamento quando criada uma nova versão.</t>
   </si>
   <si>
-    <t>11/03/2025</t>
+    <t>8668304398</t>
   </si>
   <si>
     <t>Criar tela específica para analista/engenheiro realizar inspeção.</t>
   </si>
   <si>
+    <t>16/03/2025</t>
+  </si>
+  <si>
+    <t>8668305089</t>
+  </si>
+  <si>
     <t>Criar novo PDI caso o analista/engenherio indicar retrabalhar</t>
   </si>
   <si>
+    <t>8668306068</t>
+  </si>
+  <si>
     <t>Permitir inspetor visualizar instrução do analista/engenheiro</t>
   </si>
   <si>
+    <t>8668306622</t>
+  </si>
+  <si>
     <t>PDI para avaliação do analista/inspetor, mostar apenas a cota com problema.</t>
   </si>
   <si>
+    <t>8668307091</t>
+  </si>
+  <si>
     <t>PDI gerado pelo analista/engenheiro, retrabalho, mostar apenas a cota específica para o inspetor.</t>
   </si>
   <si>
-    <t>30758</t>
+    <t>8668562921</t>
   </si>
   <si>
     <t>Indefinido</t>
@@ -315,37 +348,31 @@
     <t>Cadastrar códigos de parada para o JATO GANCHEIRA</t>
   </si>
   <si>
-    <t>30465</t>
+    <t>8671462851</t>
   </si>
   <si>
     <t>Irog ajustagem 2</t>
   </si>
   <si>
-    <t>30539</t>
+    <t>8689082066</t>
   </si>
   <si>
     <t>Irog ajustagem 3</t>
   </si>
   <si>
-    <t>13/03/2025</t>
-  </si>
-  <si>
-    <t>30600</t>
+    <t>8716813366</t>
   </si>
   <si>
     <t>Apontamento Ajustagem</t>
   </si>
   <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>30087</t>
+    <t>8657840229</t>
   </si>
   <si>
     <t>Ajustes do apontamento individual e registros da USE</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>8584305408</t>
   </si>
   <si>
     <t>Melhorar a parte visual ao apresentar os horários disponíveis no calendário, pois atualmente está sobrepondo</t>
@@ -357,7 +384,7 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>30198</t>
+    <t>8539762729</t>
   </si>
   <si>
     <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELTRONICOS</t>
@@ -369,18 +396,24 @@
     <t>Definir responsável da KB</t>
   </si>
   <si>
-    <t>30379</t>
+    <t>8657940627</t>
   </si>
   <si>
     <t>Grid com contador de produção de hora em hora, conforme layout atual</t>
   </si>
   <si>
+    <t>8657940805</t>
+  </si>
+  <si>
     <t>Atualizar card de produção diária</t>
   </si>
   <si>
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Criação do grupo d recursos roteiro CPP</t>
   </si>
   <si>
@@ -396,6 +429,9 @@
     <t>19/05/2026</t>
   </si>
   <si>
+    <t>8657940714</t>
+  </si>
+  <si>
     <t>Informar quantidade produzida por hora  (piso e vagonete)</t>
   </si>
   <si>
@@ -408,12 +444,18 @@
     <t>Inclusão de setor no MRP de materiais</t>
   </si>
   <si>
+    <t>8648101903</t>
+  </si>
+  <si>
     <t>Diário de bordo moldagem</t>
   </si>
   <si>
     <t>30069</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Sistema de Controle de Importação</t>
   </si>
   <si>
@@ -423,7 +465,10 @@
     <t>Djalma Machado</t>
   </si>
   <si>
-    <t>22847</t>
+    <t>23/03/2025</t>
+  </si>
+  <si>
+    <t>8582847582</t>
   </si>
   <si>
     <t>Publicar WebService movimentação de peças</t>
@@ -444,25 +489,25 @@
     <t>24/02/2025</t>
   </si>
   <si>
-    <t>30081</t>
+    <t>8657705110</t>
   </si>
   <si>
     <t>INVENTÁRIO WMS</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8657820395</t>
   </si>
   <si>
     <t>Atualização das parcelas programadas - Carga do Programado para evento - Treinamento Comercial</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>8657782807</t>
   </si>
   <si>
     <t>QVD - Faturamento (Contas a receber)</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>8674764228</t>
   </si>
   <si>
     <t>IROG Apontamento jatos</t>
@@ -474,9 +519,6 @@
     <t>Criar uma tabela no ERP para gerar as OP's de integração com o APS, gravar nessa tabela todas as informações necessárias para a integração, gerar automaticamente o código da OP.</t>
   </si>
   <si>
-    <t>19/03/2025</t>
-  </si>
-  <si>
     <t>Criar um nível na tabela de OP para se gerar o roteiro/fluxo dos itens para integração buscando a ultima revisão do CPP</t>
   </si>
   <si>
@@ -489,12 +531,18 @@
     <t>Envio necessidade de materiais APS</t>
   </si>
   <si>
+    <t>8753541582</t>
+  </si>
+  <si>
     <t>Retirar os eventos e funcionalidades não utilizadas</t>
   </si>
   <si>
     <t>21/03/2025</t>
   </si>
   <si>
+    <t>8753568049</t>
+  </si>
+  <si>
     <t>Na tela de login do fornecedor, inserir um campo do tipo data</t>
   </si>
   <si>
@@ -504,7 +552,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-6</t>
+    <t>Jul/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1146,13 +1194,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -1193,7 +1241,7 @@
         <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1202,7 +1250,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>35</v>
@@ -1210,7 +1258,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1222,10 +1270,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1240,7 +1288,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1257,7 +1305,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1269,10 +1317,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1287,7 +1335,7 @@
         <v>38</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1296,7 +1344,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>35</v>
@@ -1304,22 +1352,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1334,7 +1382,7 @@
         <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1351,7 +1399,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1363,10 +1411,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1381,7 +1429,7 @@
         <v>31</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1398,7 +1446,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1410,10 +1458,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1425,10 +1473,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1437,15 +1485,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1457,10 +1505,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1484,7 +1532,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>35</v>
@@ -1492,7 +1540,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1504,10 +1552,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1522,7 +1570,7 @@
         <v>38</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1531,7 +1579,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>35</v>
@@ -1539,22 +1587,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1569,7 +1617,7 @@
         <v>31</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1586,7 +1634,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1598,10 +1646,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1616,7 +1664,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1633,7 +1681,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1645,10 +1693,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1680,37 +1728,37 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1727,7 +1775,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1739,10 +1787,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1766,7 +1814,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>35</v>
@@ -1774,37 +1822,37 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1821,7 +1869,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1833,10 +1881,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1851,7 +1899,7 @@
         <v>31</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1868,7 +1916,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1880,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1907,7 +1955,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>35</v>
@@ -1915,7 +1963,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1927,10 +1975,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1945,7 +1993,7 @@
         <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1962,7 +2010,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1974,10 +2022,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1992,7 +2040,7 @@
         <v>38</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2001,7 +2049,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>35</v>
@@ -2009,7 +2057,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2021,10 +2069,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2039,7 +2087,7 @@
         <v>31</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2056,7 +2104,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2068,13 +2116,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -2086,7 +2134,7 @@
         <v>38</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2095,7 +2143,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -2103,7 +2151,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2115,10 +2163,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2142,7 +2190,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>35</v>
@@ -2150,7 +2198,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2162,10 +2210,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2177,10 +2225,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2197,7 +2245,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2209,10 +2257,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2224,10 +2272,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2244,7 +2292,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2256,10 +2304,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2271,10 +2319,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2291,7 +2339,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2303,10 +2351,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2318,10 +2366,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2338,7 +2386,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2350,10 +2398,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2365,10 +2413,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2385,7 +2433,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2397,10 +2445,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2412,10 +2460,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2432,22 +2480,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2459,10 +2507,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2479,22 +2527,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2506,10 +2554,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2526,22 +2574,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2553,10 +2601,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2573,22 +2621,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2600,10 +2648,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2620,7 +2668,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2632,10 +2680,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2667,7 +2715,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2679,10 +2727,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2694,10 +2742,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2706,7 +2754,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2714,7 +2762,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2726,10 +2774,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2744,13 +2792,13 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2761,7 +2809,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2773,13 +2821,13 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -2791,7 +2839,7 @@
         <v>31</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2808,7 +2856,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2820,10 +2868,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2838,7 +2886,7 @@
         <v>31</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2855,7 +2903,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2867,10 +2915,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2885,7 +2933,7 @@
         <v>31</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2902,37 +2950,37 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2949,7 +2997,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2961,10 +3009,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2979,7 +3027,7 @@
         <v>31</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2996,7 +3044,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3008,10 +3056,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3026,7 +3074,7 @@
         <v>38</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3035,7 +3083,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>35</v>
@@ -3043,37 +3091,37 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3090,7 +3138,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3102,10 +3150,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3123,13 +3171,13 @@
         <v>24</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>35</v>
@@ -3137,37 +3185,37 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3184,25 +3232,25 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>21</v>
@@ -3211,19 +3259,19 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3231,37 +3279,37 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3270,7 +3318,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3278,7 +3326,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3290,10 +3338,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3308,13 +3356,13 @@
         <v>31</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>34</v>
@@ -3325,25 +3373,25 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>21</v>
@@ -3355,7 +3403,7 @@
         <v>31</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3372,7 +3420,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3384,13 +3432,13 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>21</v>
@@ -3405,10 +3453,10 @@
         <v>24</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>34</v>
@@ -3419,25 +3467,25 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>21</v>
@@ -3446,10 +3494,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3466,37 +3514,37 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3513,37 +3561,37 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3560,37 +3608,37 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3607,43 +3655,43 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>27</v>
@@ -3654,37 +3702,37 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3701,37 +3749,37 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3748,7 +3796,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>110</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3760,10 +3808,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3775,10 +3823,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -3795,7 +3843,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3807,10 +3855,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3822,10 +3870,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -3853,23 +3901,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3877,16 +3925,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3897,15 +3945,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>422.6</v>
+        <v>92.46</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3918,7 +3966,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3926,7 +3974,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3957,12 +4005,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B2">
         <v>59</v>
@@ -3976,35 +4024,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>422.6</v>
+        <v>92.46</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4012,7 +4060,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4021,13 +4069,13 @@
         <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4039,21 +4087,27 @@
         <v>52</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -4062,24 +4116,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -4091,59 +4151,59 @@
         <v>50</v>
       </c>
       <c r="J12" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="Q12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
-      <c r="P13" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4151,7 +4211,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -4159,7 +4219,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4167,7 +4227,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4175,10 +4235,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4186,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4194,142 +4254,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>435</v>
+        <v>698</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>140</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>421</v>
+        <v>698</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>421</v>
+        <v>698</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>421</v>
+        <v>698</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>412</v>
+        <v>698</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>412</v>
+        <v>698</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="F27" s="2">
-        <v>412</v>
+        <v>698</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="F28" s="2">
-        <v>412</v>
+        <v>670</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="F29" s="2">
-        <v>365</v>
+        <v>670</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="F30" s="2">
-        <v>365</v>
+        <v>670</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
